--- a/data/elections/Data_Election.xlsx
+++ b/data/elections/Data_Election.xlsx
@@ -10945,7 +10945,7 @@
         <v>41461</v>
       </c>
       <c r="J198" s="144" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K198">
         <v>785</v>

--- a/data/elections/Data_Election.xlsx
+++ b/data/elections/Data_Election.xlsx
@@ -10441,7 +10441,7 @@
         <v>52857</v>
       </c>
       <c r="J184" s="144" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K184">
         <v>940</v>
@@ -10945,7 +10945,7 @@
         <v>41461</v>
       </c>
       <c r="J198" s="144" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K198">
         <v>785</v>
